--- a/Liga 2026-27/laliga_2627_v4.xlsx
+++ b/Liga 2026-27/laliga_2627_v4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan\Documents\Cromos\Liga 2026-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A187C0-109C-4007-B9C1-A531F7ACC88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3506CB-5119-4B76-B20A-6E59E3642506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="14" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="15" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -3400,7 +3400,7 @@
     <xf numFmtId="0" fontId="10" fillId="47" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3410,7 +3410,7 @@
     <xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4211,11 +4211,11 @@
       </c>
       <c r="C17" s="4">
         <f>COUNTIF('R. RACING CLUB'!C3:C27,"")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="5">
         <f>COUNTIF('R. RACING CLUB'!D3:D27,"X")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="6">
         <f>SUMIF('R. RACING CLUB'!E3:E27,"&gt;"&amp;0,'R. RACING CLUB'!E3:E27)</f>
@@ -4323,11 +4323,11 @@
       </c>
       <c r="C21" s="4">
         <f>COUNTIF('VALENCIA CF'!C3:C26,"")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" s="5">
         <f>COUNTIF('VALENCIA CF'!D3:D26,"X")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="6">
         <f>SUMIF('VALENCIA CF'!E3:E26,"&gt;"&amp;0,'VALENCIA CF'!E3:E26)</f>
@@ -4547,11 +4547,11 @@
       </c>
       <c r="C29" s="29">
         <f>COUNTIF('ÚLTIMOS FICHAJES'!C3:C42,"")</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D29" s="30">
         <f>COUNTIF('ÚLTIMOS FICHAJES'!D3:D42,"X")</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E29" s="31">
         <f>SUMIF('ÚLTIMOS FICHAJES'!E3:E42,"&gt;"&amp;0,'ÚLTIMOS FICHAJES'!E3:E42)</f>
@@ -4576,11 +4576,11 @@
       </c>
       <c r="C30" s="13">
         <f t="shared" si="0"/>
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D30" s="14">
         <f t="shared" si="0"/>
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E30" s="15">
         <f t="shared" si="0"/>
@@ -7197,7 +7197,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="75" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="76"/>
@@ -7850,10 +7850,10 @@
       <c r="B9" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="C9" s="60"/>
-      <c r="D9" s="72" t="s">
-        <v>10</v>
-      </c>
+      <c r="C9" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="72"/>
       <c r="E9" s="62"/>
       <c r="F9" s="63"/>
       <c r="G9" s="64">
@@ -10599,10 +10599,10 @@
       <c r="B20" s="53" t="s">
         <v>515</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="37" t="s">
-        <v>10</v>
-      </c>
+      <c r="C20" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="37"/>
       <c r="E20" s="38"/>
       <c r="F20" s="39"/>
       <c r="G20" s="40">
@@ -11607,10 +11607,10 @@
       <c r="B20" s="66" t="s">
         <v>585</v>
       </c>
-      <c r="C20" s="60"/>
-      <c r="D20" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C20" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="61"/>
       <c r="E20" s="62"/>
       <c r="F20" s="63"/>
       <c r="G20" s="64">
@@ -15454,7 +15454,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="75" t="s">
         <v>60</v>
       </c>
       <c r="B1" s="76"/>
@@ -15993,7 +15993,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="75" t="s">
         <v>61</v>
       </c>
       <c r="B1" s="76"/>
@@ -16510,7 +16510,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="79" t="s">
         <v>62</v>
       </c>
       <c r="B1" s="76"/>

--- a/Liga 2026-27/laliga_2627_v4.xlsx
+++ b/Liga 2026-27/laliga_2627_v4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan\Documents\Cromos\Liga 2026-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3506CB-5119-4B76-B20A-6E59E3642506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9F3959-A852-4BD7-911B-454018E91CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="15" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="18" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -3400,7 +3400,7 @@
     <xf numFmtId="0" fontId="10" fillId="47" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3408,6 +3408,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3420,9 +3423,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4547,11 +4547,11 @@
       </c>
       <c r="C29" s="29">
         <f>COUNTIF('ÚLTIMOS FICHAJES'!C3:C42,"")</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D29" s="30">
         <f>COUNTIF('ÚLTIMOS FICHAJES'!D3:D42,"X")</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E29" s="31">
         <f>SUMIF('ÚLTIMOS FICHAJES'!E3:E42,"&gt;"&amp;0,'ÚLTIMOS FICHAJES'!E3:E42)</f>
@@ -4576,11 +4576,11 @@
       </c>
       <c r="C30" s="13">
         <f t="shared" si="0"/>
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D30" s="14">
         <f t="shared" si="0"/>
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E30" s="15">
         <f t="shared" si="0"/>
@@ -4632,7 +4632,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="83" t="s">
         <v>66</v>
       </c>
       <c r="B1" s="76"/>
@@ -6702,7 +6702,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="83" t="s">
         <v>70</v>
       </c>
       <c r="B1" s="76"/>
@@ -7197,7 +7197,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="79" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="76"/>
@@ -7700,7 +7700,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="75" t="s">
         <v>72</v>
       </c>
       <c r="B1" s="76"/>
@@ -8746,7 +8746,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="83" t="s">
         <v>74</v>
       </c>
       <c r="B1" s="76"/>
@@ -11391,10 +11391,10 @@
       <c r="B8" s="66" t="s">
         <v>561</v>
       </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C8" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="61"/>
       <c r="E8" s="62"/>
       <c r="F8" s="63"/>
       <c r="G8" s="64">
@@ -11499,10 +11499,10 @@
       <c r="B14" s="66" t="s">
         <v>573</v>
       </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C14" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="61"/>
       <c r="E14" s="62"/>
       <c r="F14" s="63"/>
       <c r="G14" s="64">
@@ -11643,10 +11643,10 @@
       <c r="B22" s="66" t="s">
         <v>589</v>
       </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="61" t="s">
-        <v>10</v>
-      </c>
+      <c r="C22" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="61"/>
       <c r="E22" s="62"/>
       <c r="F22" s="63"/>
       <c r="G22" s="64">
@@ -15454,7 +15454,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="79" t="s">
         <v>60</v>
       </c>
       <c r="B1" s="76"/>
@@ -15993,7 +15993,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="79" t="s">
         <v>61</v>
       </c>
       <c r="B1" s="76"/>
@@ -16510,7 +16510,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="80" t="s">
         <v>62</v>
       </c>
       <c r="B1" s="76"/>
@@ -16989,7 +16989,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="76"/>
@@ -17484,7 +17484,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="82" t="s">
         <v>63</v>
       </c>
       <c r="B1" s="76"/>
@@ -17993,7 +17993,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="83" t="s">
         <v>64</v>
       </c>
       <c r="B1" s="76"/>
@@ -18488,7 +18488,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="75" t="s">
         <v>65</v>
       </c>
       <c r="B1" s="76"/>
